--- a/data/trans_dic/P55$pareja-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P55$pareja-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>43,52; 61,62</t>
+          <t>42,21; 61,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,19; 49,52</t>
+          <t>30,62; 49,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,33; 51,4</t>
+          <t>31,98; 50,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,56; 41,49</t>
+          <t>25,54; 41,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 15,87</t>
+          <t>7,26; 15,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,25; 20,27</t>
+          <t>11,13; 20,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,03; 20,73</t>
+          <t>9,69; 20,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 13,59</t>
+          <t>8,02; 13,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,22; 30,13</t>
+          <t>19,82; 29,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,25; 28,55</t>
+          <t>18,53; 28,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,13; 27,88</t>
+          <t>18,22; 28,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,23; 20,46</t>
+          <t>14,17; 19,98</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,14; 65,58</t>
+          <t>14,04; 65,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,34; 65,45</t>
+          <t>18,5; 65,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,87; 63,84</t>
+          <t>26,99; 67,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,69; 46,2</t>
+          <t>23,08; 45,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,19</t>
+          <t>0,0; 36,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,12; 42,38</t>
+          <t>4,57; 40,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,63; 45,44</t>
+          <t>15,67; 42,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,69; 26,38</t>
+          <t>11,72; 25,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,52; 42,61</t>
+          <t>9,92; 41,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,82; 44,49</t>
+          <t>16,25; 45,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23,36; 47,68</t>
+          <t>22,36; 46,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,55; 31,79</t>
+          <t>18,48; 31,8</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,89</t>
+          <t>0,0; 69,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,37; 74,53</t>
+          <t>31,84; 74,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,78</t>
+          <t>0,0; 48,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,32 +1027,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,06</t>
+          <t>0,0; 67,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 32,63</t>
+          <t>4,75; 31,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 44,74</t>
+          <t>4,71; 42,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,06</t>
+          <t>0,0; 69,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,81; 77,08</t>
+          <t>13,66; 78,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,65; 49,6</t>
+          <t>21,31; 49,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,63; 56,61</t>
+          <t>40,84; 57,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,16; 49,13</t>
+          <t>30,49; 47,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,42; 52,5</t>
+          <t>35,67; 53,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,64; 41,83</t>
+          <t>29,02; 41,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 15,62</t>
+          <t>7,21; 15,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,76; 20,76</t>
+          <t>11,55; 20,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,73; 22,81</t>
+          <t>12,59; 23,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,58; 14,81</t>
+          <t>9,55; 14,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,12; 28,97</t>
+          <t>19,7; 29,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,74; 28,49</t>
+          <t>19,47; 28,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,5; 30,55</t>
+          <t>21,2; 30,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,04; 22,6</t>
+          <t>16,85; 22,28</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44839; 63488</t>
+          <t>43484; 63017</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37477; 61469</t>
+          <t>38002; 61327</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30221; 48036</t>
+          <t>29893; 47369</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25941; 40516</t>
+          <t>24938; 40117</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15249; 32678</t>
+          <t>14937; 32261</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28229; 50850</t>
+          <t>27919; 51093</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20923; 43237</t>
+          <t>20212; 43286</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20884; 35018</t>
+          <t>20677; 34799</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62449; 93062</t>
+          <t>61227; 91048</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>72175; 107057</t>
+          <t>69473; 105176</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54765; 84210</t>
+          <t>55016; 84878</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50570; 72705</t>
+          <t>50350; 71003</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2149; 9305</t>
+          <t>1992; 9313</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3872; 13101</t>
+          <t>3704; 13137</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6147; 14605</t>
+          <t>6175; 15383</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10193; 19876</t>
+          <t>9928; 19405</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3940</t>
+          <t>0; 4969</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1083; 8965</t>
+          <t>967; 8480</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8135; 23646</t>
+          <t>8152; 21905</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6389; 14418</t>
+          <t>6406; 14121</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2913; 11796</t>
+          <t>2746; 11397</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6925; 18316</t>
+          <t>6690; 18726</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17499; 35719</t>
+          <t>16755; 34814</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18120; 31051</t>
+          <t>18050; 31062</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6732</t>
+          <t>0; 6462</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1154</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5046; 11269</t>
+          <t>4815; 11309</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5413</t>
+          <t>0; 5657</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1950,32 +1950,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4400</t>
+          <t>0; 4543</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>624; 4564</t>
+          <t>664; 4443</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>948; 9367</t>
+          <t>987; 8804</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4391</t>
+          <t>0; 4454</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1760; 9157</t>
+          <t>1622; 9327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6592; 14437</t>
+          <t>6203; 14482</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51428; 71659</t>
+          <t>51690; 72241</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45551; 71809</t>
+          <t>44567; 69964</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43026; 63764</t>
+          <t>43323; 64488</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47737; 65162</t>
+          <t>45207; 64608</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16804; 36065</t>
+          <t>16649; 34700</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32514; 57391</t>
+          <t>31937; 56779</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34048; 60975</t>
+          <t>33670; 62436</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31260; 48324</t>
+          <t>31173; 47742</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71914; 103582</t>
+          <t>70432; 104258</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>83414; 120415</t>
+          <t>82290; 119926</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83602; 118789</t>
+          <t>82445; 117938</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82135; 108965</t>
+          <t>81242; 107435</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$pareja-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P55$pareja-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,21; 61,17</t>
+          <t>43,45; 61,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,62; 49,41</t>
+          <t>30,35; 50,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,98; 50,68</t>
+          <t>33,08; 51,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,54; 41,08</t>
+          <t>25,48; 41,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 15,67</t>
+          <t>7,13; 16,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,13; 20,37</t>
+          <t>10,91; 20,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,69; 20,75</t>
+          <t>9,75; 20,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,02; 13,51</t>
+          <t>8,14; 13,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,82; 29,48</t>
+          <t>20,2; 30,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,53; 28,05</t>
+          <t>18,83; 28,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,22; 28,1</t>
+          <t>18,16; 27,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,17; 19,98</t>
+          <t>14,13; 19,98</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,04; 65,64</t>
+          <t>16,64; 62,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,5; 65,64</t>
+          <t>19,19; 64,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,99; 67,25</t>
+          <t>27,74; 65,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,08; 45,11</t>
+          <t>23,26; 45,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,81</t>
+          <t>0,0; 33,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 40,09</t>
+          <t>4,61; 40,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,67; 42,09</t>
+          <t>16,18; 43,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 25,83</t>
+          <t>12,41; 27,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,92; 41,16</t>
+          <t>9,81; 43,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,25; 45,49</t>
+          <t>17,46; 44,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,36; 46,47</t>
+          <t>22,76; 45,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,48; 31,8</t>
+          <t>18,94; 32,08</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,0</t>
+          <t>0,0; 74,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,84; 100,0</t>
+          <t>21,88; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,84; 74,8</t>
+          <t>36,83; 77,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,89</t>
+          <t>0,0; 48,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 76,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,18</t>
+          <t>0,0; 60,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 31,77</t>
+          <t>6,83; 36,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 42,05</t>
+          <t>4,83; 46,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,03</t>
+          <t>0,0; 69,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,66; 78,51</t>
+          <t>12,59; 75,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,31; 49,76</t>
+          <t>26,02; 52,07</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,84; 57,07</t>
+          <t>39,28; 58,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,49; 47,87</t>
+          <t>30,9; 49,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,67; 53,09</t>
+          <t>36,68; 53,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,02; 41,47</t>
+          <t>30,54; 42,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 15,03</t>
+          <t>7,31; 15,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,55; 20,54</t>
+          <t>11,46; 20,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,59; 23,35</t>
+          <t>12,79; 22,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,55; 14,63</t>
+          <t>9,92; 15,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,7; 29,16</t>
+          <t>19,94; 28,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,47; 28,38</t>
+          <t>19,71; 28,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,2; 30,33</t>
+          <t>20,94; 30,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,85; 22,28</t>
+          <t>17,72; 23,14</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32696</t>
+          <t>35289</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27581</t>
+          <t>29529</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60277</t>
+          <t>64818</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43484; 63017</t>
+          <t>44766; 63800</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38002; 61327</t>
+          <t>37678; 62392</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29893; 47369</t>
+          <t>30914; 48488</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24938; 40117</t>
+          <t>26437; 42805</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14937; 32261</t>
+          <t>14683; 33744</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27919; 51093</t>
+          <t>27378; 51619</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20212; 43286</t>
+          <t>20330; 42899</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20677; 34799</t>
+          <t>22532; 37884</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61227; 91048</t>
+          <t>62400; 93468</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>69473; 105176</t>
+          <t>70618; 106676</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55016; 84878</t>
+          <t>54843; 83966</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50350; 71003</t>
+          <t>53795; 76035</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24483</t>
+          <t>28108</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1992; 9313</t>
+          <t>2361; 8811</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3704; 13137</t>
+          <t>3841; 12930</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6175; 15383</t>
+          <t>6346; 14919</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9928; 19405</t>
+          <t>11009; 21641</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4969</t>
+          <t>0; 4473</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>967; 8480</t>
+          <t>975; 8600</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8152; 21905</t>
+          <t>8420; 22726</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6406; 14121</t>
+          <t>7777; 17293</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2746; 11397</t>
+          <t>2717; 12002</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6690; 18726</t>
+          <t>7189; 18283</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16755; 34814</t>
+          <t>17055; 34189</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18050; 31062</t>
+          <t>20824; 35283</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>12426</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6462</t>
+          <t>0; 6979</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1930,52 +1930,52 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1629; 5118</t>
+          <t>1120; 5118</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4815; 11309</t>
+          <t>6103; 12866</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5657</t>
+          <t>0; 5629</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4423</t>
+          <t>0; 3397</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4543</t>
+          <t>0; 4088</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>664; 4443</t>
+          <t>1075; 5762</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>987; 8804</t>
+          <t>1010; 9745</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4454</t>
+          <t>0; 4510</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1622; 9327</t>
+          <t>1496; 8977</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6203; 14482</t>
+          <t>8410; 16828</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55616</t>
+          <t>61168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>39474</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95090</t>
+          <t>105353</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51690; 72241</t>
+          <t>49719; 73993</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44567; 69964</t>
+          <t>45161; 71663</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43323; 64488</t>
+          <t>44557; 64999</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45207; 64608</t>
+          <t>51203; 70926</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16649; 34700</t>
+          <t>16892; 35436</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31937; 56779</t>
+          <t>31669; 56775</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33670; 62436</t>
+          <t>34196; 60696</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31173; 47742</t>
+          <t>35243; 53717</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70432; 104258</t>
+          <t>71300; 103352</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>82290; 119926</t>
+          <t>83299; 122030</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82445; 117938</t>
+          <t>81430; 119400</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>81242; 107435</t>
+          <t>92665; 120978</t>
         </is>
       </c>
     </row>
